--- a/outputs/567-21.xlsx
+++ b/outputs/567-21.xlsx
@@ -56,11 +56,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm"/>
     <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -139,23 +138,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -348,31 +347,33 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A3:G28"/>
+  <dimension ref="A3:G10"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="8.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.71"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="4" t="n">
         <v>43586</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="5" t="n">
         <v>43964</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>104.08</v>
       </c>
     </row>
@@ -388,78 +389,86 @@
       <c r="E4" s="4" t="n">
         <v>43739</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="5" t="n">
         <v>43741</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>318.75</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="4" t="n">
         <v>43739</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="5" t="n">
         <v>43741</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="1" t="n">
         <v>23.73</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="4" t="n">
         <v>43739</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="5" t="n">
         <v>43741</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <v>19.64</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="4" t="n">
         <v>43770</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="5" t="n">
         <v>44116</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <v>62.4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4" t="n">
         <v>44105</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="5" t="n">
         <v>44116</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="1" t="n">
         <v>5.27</v>
       </c>
     </row>
@@ -475,10 +484,10 @@
       <c r="E9" s="4" t="n">
         <v>43891</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="5" t="n">
         <v>44041</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="1" t="n">
         <v>250</v>
       </c>
     </row>
@@ -494,91 +503,12 @@
       <c r="E10" s="4" t="n">
         <v>43891</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="5" t="n">
         <v>44041</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <v>60</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="2"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/outputs/567-21.xlsx
+++ b/outputs/567-21.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="14">
   <si>
     <t xml:space="preserve">1997002667</t>
   </si>
@@ -28,6 +28,12 @@
     <t xml:space="preserve">910368891</t>
   </si>
   <si>
+    <t xml:space="preserve">1997002682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">910366766</t>
+  </si>
+  <si>
     <t xml:space="preserve">1997002704</t>
   </si>
   <si>
@@ -44,6 +50,12 @@
   </si>
   <si>
     <t xml:space="preserve">910369255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1997002721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">912098175</t>
   </si>
   <si>
     <t xml:space="preserve">1997002725</t>
@@ -133,28 +145,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -347,166 +355,292 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A3:G10"/>
+  <dimension ref="A3:G18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="8.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.71"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4" t="n">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="3" t="n">
         <v>43586</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="4" t="n">
         <v>43964</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="0" t="n">
         <v>104.08</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4" t="n">
+      <c r="F4" s="4"/>
+      <c r="G4" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>43647</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>43741</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="3" t="n">
         <v>43739</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F6" s="4" t="n">
         <v>43741</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G6" s="0" t="n">
         <v>318.75</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="4" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="3" t="n">
         <v>43739</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F7" s="4" t="n">
         <v>43741</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G7" s="0" t="n">
         <v>23.73</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="4" t="n">
+      <c r="B8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="3" t="n">
         <v>43739</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F8" s="4" t="n">
         <v>43741</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G8" s="0" t="n">
         <v>19.64</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="4" t="n">
-        <v>43770</v>
-      </c>
-      <c r="F7" s="5" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>43435</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>44116</v>
       </c>
-      <c r="G7" s="1" t="n">
-        <v>62.4</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="G9" s="0" t="n">
+        <v>83.2</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="4" t="n">
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="3" t="n">
         <v>44105</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F10" s="4" t="n">
         <v>44116</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G10" s="0" t="n">
         <v>5.27</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="4" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>39126</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>43435</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>44041</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>43617</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>44041</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>43678</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>44041</v>
+      </c>
+      <c r="G14" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>43739</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>44041</v>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>44041</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="3" t="n">
         <v>43891</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F17" s="4" t="n">
         <v>44041</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G17" s="0" t="n">
         <v>250</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="4" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="3" t="n">
         <v>43891</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F18" s="4" t="n">
         <v>44041</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G18" s="0" t="n">
         <v>60</v>
       </c>
     </row>
